--- a/mygui_docking/Project1/Project1/data/ADXL355_sync_1.xlsx
+++ b/mygui_docking/Project1/Project1/data/ADXL355_sync_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10812"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Troldal/Development/bin2c/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxnkilmt\Documents\GitHub\ZJU_Oil\mygui_docking\Project1\Project1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC33A6FB-1603-2641-A40F-B7C7F2B0E698}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F286D15-B4B7-4F13-8B41-4D91C8653ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1560" windowWidth="28040" windowHeight="17440" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Time</t>
   </si>
@@ -59,33 +56,53 @@
     <t>Device 0x01 Accel Z</t>
   </si>
   <si>
-    <t>2025-07-10 13:18:28</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:29</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:30</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:31</t>
-  </si>
-  <si>
-    <t>2025-07-10 13:18:32</t>
+    <t>2025-07-14 11:19:22</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:23</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:24</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:25</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:26</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:27</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:28</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:29</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:30</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts>
-	</numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -113,7 +130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -129,7 +146,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -425,148 +442,267 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="B2">
+        <v>1.26190185546875E-2</v>
+      </c>
+      <c r="C2">
+        <v>-2.13623046875E-4</v>
+      </c>
+      <c r="D2">
+        <v>0.9764251708984375</v>
+      </c>
+      <c r="E2">
+        <v>-6.4544677734375E-3</v>
+      </c>
+      <c r="F2">
+        <v>1.57318115234375E-2</v>
+      </c>
+      <c r="G2">
+        <v>0.97943115234375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <v>-0.2133636474609375</v>
-      </c>
-      <c r="C2">
-        <v>-0.354034423828125</v>
-      </c>
-      <c r="D2">
-        <v>0.8843536376953125</v>
-      </c>
-      <c r="E2">
-        <v>-9.1552734375e-05</v>
-      </c>
-      <c r="F2">
-        <v>0.008636474609375</v>
-      </c>
-      <c r="G2">
-        <v>0.979156494140625</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>1.33514404296875E-2</v>
+      </c>
+      <c r="C3">
+        <v>-3.0517578125E-4</v>
+      </c>
+      <c r="D3">
+        <v>0.97406005859375</v>
+      </c>
+      <c r="E3">
+        <v>-6.2713623046875E-3</v>
+      </c>
+      <c r="F3">
+        <v>1.580810546875E-2</v>
+      </c>
+      <c r="G3">
+        <v>0.978973388671875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
-        <v>-0.2141876220703125</v>
-      </c>
-      <c r="C3">
-        <v>-0.3503875732421875</v>
-      </c>
-      <c r="D3">
-        <v>0.88421630859375</v>
-      </c>
-      <c r="E3">
-        <v>0.001007080078125</v>
-      </c>
-      <c r="F3">
-        <v>0.0089874267578125</v>
-      </c>
-      <c r="G3">
-        <v>0.9781341552734375</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
+      <c r="B4">
+        <v>1.27410888671875E-2</v>
+      </c>
+      <c r="C4">
+        <v>3.662109375E-4</v>
+      </c>
+      <c r="D4">
+        <v>0.9749908447265625</v>
+      </c>
+      <c r="E4">
+        <v>-5.6304931640625E-3</v>
+      </c>
+      <c r="F4">
+        <v>1.519775390625E-2</v>
+      </c>
+      <c r="G4">
+        <v>0.979217529296875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>-0.213653564453125</v>
-      </c>
-      <c r="C4">
-        <v>-0.352813720703125</v>
-      </c>
-      <c r="D4">
-        <v>0.8879547119140625</v>
-      </c>
-      <c r="E4">
-        <v>0.0002288818359375</v>
-      </c>
-      <c r="F4">
-        <v>0.008148193359375</v>
-      </c>
-      <c r="G4">
-        <v>0.9812774658203125</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
+      <c r="B5">
+        <v>1.24969482421875E-2</v>
+      </c>
+      <c r="C5">
+        <v>-6.7138671875E-4</v>
+      </c>
+      <c r="D5">
+        <v>0.97528076171875</v>
+      </c>
+      <c r="E5">
+        <v>-4.8675537109375E-3</v>
+      </c>
+      <c r="F5">
+        <v>1.55029296875E-2</v>
+      </c>
+      <c r="G5">
+        <v>0.979827880859375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
-        <v>-0.2137298583984375</v>
-      </c>
-      <c r="C5">
-        <v>-0.350860595703125</v>
-      </c>
-      <c r="D5">
-        <v>0.885009765625</v>
-      </c>
-      <c r="E5">
-        <v>-9.1552734375e-05</v>
-      </c>
-      <c r="F5">
-        <v>0.008697509765625</v>
-      </c>
-      <c r="G5">
-        <v>0.9790191650390625</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="B6">
+        <v>1.34124755859375E-2</v>
+      </c>
+      <c r="C6">
+        <v>-9.1552734375E-5</v>
+      </c>
+      <c r="D6">
+        <v>0.9747772216796875</v>
+      </c>
+      <c r="E6">
+        <v>-6.500244140625E-3</v>
+      </c>
+      <c r="F6">
+        <v>1.568603515625E-2</v>
+      </c>
+      <c r="G6">
+        <v>0.979461669921875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
-        <v>-0.214630126953125</v>
-      </c>
-      <c r="C6">
-        <v>-0.3510284423828125</v>
-      </c>
-      <c r="D6">
-        <v>0.8846435546875</v>
-      </c>
-      <c r="E6">
-        <v>-0.000457763671875</v>
-      </c>
-      <c r="F6">
-        <v>0.008697509765625</v>
-      </c>
-      <c r="G6">
-        <v>0.9808807373046875</v>
+      <c r="B7">
+        <v>1.214599609375E-2</v>
+      </c>
+      <c r="C7">
+        <v>-1.1749267578125E-3</v>
+      </c>
+      <c r="D7">
+        <v>0.975372314453125</v>
+      </c>
+      <c r="E7">
+        <v>-6.3018798828125E-3</v>
+      </c>
+      <c r="F7">
+        <v>1.49993896484375E-2</v>
+      </c>
+      <c r="G7">
+        <v>0.980743408203125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>1.30462646484375E-2</v>
+      </c>
+      <c r="C8">
+        <v>4.119873046875E-4</v>
+      </c>
+      <c r="D8">
+        <v>0.975738525390625</v>
+      </c>
+      <c r="E8">
+        <v>-5.7220458984375E-3</v>
+      </c>
+      <c r="F8">
+        <v>1.5167236328125E-2</v>
+      </c>
+      <c r="G8">
+        <v>0.979339599609375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>1.28326416015625E-2</v>
+      </c>
+      <c r="C9">
+        <v>1.220703125E-4</v>
+      </c>
+      <c r="D9">
+        <v>0.97509765625</v>
+      </c>
+      <c r="E9">
+        <v>-6.2255859375E-3</v>
+      </c>
+      <c r="F9">
+        <v>1.49383544921875E-2</v>
+      </c>
+      <c r="G9">
+        <v>0.981658935546875</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>1.24664306640625E-2</v>
+      </c>
+      <c r="C10">
+        <v>-4.57763671875E-5</v>
+      </c>
+      <c r="D10">
+        <v>0.9748382568359375</v>
+      </c>
+      <c r="E10">
+        <v>-5.7220458984375E-3</v>
+      </c>
+      <c r="F10">
+        <v>1.59759521484375E-2</v>
+      </c>
+      <c r="G10">
+        <v>0.9805908203125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>1.3702392578125E-2</v>
+      </c>
+      <c r="C11">
+        <v>-8.087158203125E-4</v>
+      </c>
+      <c r="D11">
+        <v>0.9761505126953125</v>
+      </c>
+      <c r="E11">
+        <v>-7.14111328125E-3</v>
+      </c>
+      <c r="F11">
+        <v>1.52740478515625E-2</v>
+      </c>
+      <c r="G11">
+        <v>0.980224609375</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/mygui_docking/Project1/Project1/data/ADXL355_sync_1.xlsx
+++ b/mygui_docking/Project1/Project1/data/ADXL355_sync_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mxnkilmt\Documents\GitHub\ZJU_Oil\mygui_docking\Project1\Project1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F286D15-B4B7-4F13-8B41-4D91C8653ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8AF785-0C37-4FC4-AF86-39092665709B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{FF49B81A-127A-B44C-A44B-FF0F3EF8FCF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,57 +33,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Device 0x00 Accel Y</t>
+  </si>
+  <si>
+    <t>Device 0x00 Accel Z</t>
+  </si>
+  <si>
+    <t>Device 0x01 Accel X</t>
+  </si>
+  <si>
+    <t>Device 0x01 Accel Y</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:22</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:23</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:24</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:25</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:26</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:27</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:28</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:29</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:30</t>
+  </si>
+  <si>
+    <t>2025-07-14 11:19:31</t>
+  </si>
+  <si>
+    <t>Device 0x01 Accel Z</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device 0x00 Accel X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传感器地址</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>Time</t>
-  </si>
-  <si>
-    <t>Device 0x00 Accel X</t>
-  </si>
-  <si>
-    <t>Device 0x00 Accel Y</t>
-  </si>
-  <si>
-    <t>Device 0x00 Accel Z</t>
-  </si>
-  <si>
-    <t>Device 0x01 Accel X</t>
-  </si>
-  <si>
-    <t>Device 0x01 Accel Y</t>
-  </si>
-  <si>
-    <t>Device 0x01 Accel Z</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:22</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:23</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:24</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:25</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:26</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:27</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:28</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:29</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:30</t>
-  </si>
-  <si>
-    <t>2025-07-14 11:19:31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -442,38 +457,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049FB1B4-2A61-4643-8816-8B76EC36FD4B}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="10.87890625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.90625" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="18.87890625" customWidth="1"/>
+    <col min="3" max="3" width="17.05859375" customWidth="1"/>
+    <col min="6" max="7" width="17.64453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>7</v>
       </c>
       <c r="B2">
         <v>1.26190185546875E-2</v>
@@ -494,9 +512,9 @@
         <v>0.97943115234375</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1.33514404296875E-2</v>
@@ -517,9 +535,9 @@
         <v>0.978973388671875</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>1.27410888671875E-2</v>
@@ -540,9 +558,9 @@
         <v>0.979217529296875</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1.24969482421875E-2</v>
@@ -563,9 +581,9 @@
         <v>0.979827880859375</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>1.34124755859375E-2</v>
@@ -586,9 +604,9 @@
         <v>0.979461669921875</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1.214599609375E-2</v>
@@ -609,9 +627,9 @@
         <v>0.980743408203125</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>1.30462646484375E-2</v>
@@ -632,9 +650,9 @@
         <v>0.979339599609375</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>1.28326416015625E-2</v>
@@ -655,9 +673,9 @@
         <v>0.981658935546875</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>1.24664306640625E-2</v>
@@ -678,9 +696,9 @@
         <v>0.9805908203125</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>1.3702392578125E-2</v>
@@ -699,6 +717,17 @@
       </c>
       <c r="G11">
         <v>0.980224609375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
